--- a/Orçado/Orça-Pecuária/JOIA - PECUÁRIA.xlsx
+++ b/Orçado/Orça-Pecuária/JOIA - PECUÁRIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Pecuária\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80FF15E-39EF-4582-A62A-E2DE5E7D6D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB4BC32-3CB3-471D-91C3-12B862164F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{71719C78-F8CA-4FAD-8CAF-576BD048F763}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{71719C78-F8CA-4FAD-8CAF-576BD048F763}"/>
   </bookViews>
   <sheets>
     <sheet name="JOIA" sheetId="1" r:id="rId1"/>
@@ -1100,7 +1100,8 @@
         <v>62700</v>
       </c>
       <c r="J6" s="10">
-        <v>52250</v>
+        <f>52250+15000</f>
+        <v>67250</v>
       </c>
       <c r="K6" s="10">
         <v>99275</v>
@@ -1288,7 +1289,8 @@
         <v>52250</v>
       </c>
       <c r="J10" s="10">
-        <v>156750</v>
+        <f>156750-83000</f>
+        <v>73750</v>
       </c>
       <c r="K10" s="10">
         <v>104500</v>
@@ -2320,7 +2322,8 @@
         <v>2524.0512000000003</v>
       </c>
       <c r="J32" s="10">
-        <v>5225</v>
+        <f>5225+54166.67</f>
+        <v>59391.67</v>
       </c>
       <c r="K32" s="10">
         <v>6270</v>
